--- a/Generators/Experiment with utility data leak/diffusion_dataleak/2. Alzhimers/TRTR_TSTR_results.xlsx
+++ b/Generators/Experiment with utility data leak/diffusion_dataleak/2. Alzhimers/TRTR_TSTR_results.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TRTR_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="All_Comparisons" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="TabDDPM" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ForestDiffusion" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRTR_Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Comparisons" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TabDDPM" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ForestDiffusion" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,255 +502,255 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SVM-RBF</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9573333333333333</v>
+        <v>0.9857142857142858</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01959591794226543</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9549442804586885</v>
+        <v>0.984126984126984</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02156270877056382</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9886418351124234</v>
+        <v>0.96875</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01392151593083359</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9243243243243244</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03783783783783785</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.9573 ± 0.0196</t>
+          <t>0.9857 ± 0.0000</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.9549 ± 0.0216</t>
+          <t>0.9841 ± 0.0000</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.9886 ± 0.0139</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.9243 ± 0.0378</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM-RBF</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9559999999999998</v>
+        <v>0.9857142857142858</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02235073948565364</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9533200486764233</v>
+        <v>0.984126984126984</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02507909177402514</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9886418351124234</v>
+        <v>0.96875</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01392151593083359</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9216216216216218</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04432762018069385</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.9560 ± 0.0224</t>
+          <t>0.9857 ± 0.0000</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.9533 ± 0.0251</t>
+          <t>0.9841 ± 0.0000</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.9886 ± 0.0139</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.9216 ± 0.0443</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9546666666666667</v>
+        <v>0.9771428571428572</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0170749979664876</v>
+        <v>0.006998542122237681</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9526820073843034</v>
+        <v>0.9749007936507936</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01853939000672906</v>
+        <v>0.007533152978797446</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9775705964096056</v>
+        <v>0.9511363636363637</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01630136615858147</v>
+        <v>0.01438147386861333</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9297297297297298</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03243243243243243</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.9547 ± 0.0171</t>
+          <t>0.9771 ± 0.0070</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.9527 ± 0.0185</t>
+          <t>0.9749 ± 0.0075</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.9776 ± 0.0163</t>
+          <t>0.9511 ± 0.0144</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.9297 ± 0.0324</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9533333333333331</v>
+        <v>0.9714285714285713</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01366260102127946</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9513798805474434</v>
+        <v>0.96875</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01493412066788913</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9752040740430834</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01902222469328762</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9297297297297298</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03243243243243243</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.9533 ± 0.0137</t>
+          <t>0.9714 ± 0.0000</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.9514 ± 0.0149</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.9752 ± 0.0190</t>
+          <t>0.9394 ± 0.0000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.9297 ± 0.0324</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>GradientBoost</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9493333333333334</v>
+        <v>0.9714285714285713</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0258542925728871</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9471443985093639</v>
+        <v>0.96875</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02807031046294366</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9674413598097809</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02864768705787136</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9297297297297298</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05012766754322002</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.9493 ± 0.0259</t>
+          <t>0.9714 ± 0.0000</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.9471 ± 0.0281</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.9674 ± 0.0286</t>
+          <t>0.9394 ± 0.0000</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.9297 ± 0.0501</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
     </row>
@@ -761,98 +761,98 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9479999999999998</v>
+        <v>0.9585714285714285</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01627540748764492</v>
+        <v>0.007693092581620716</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9457327984769963</v>
+        <v>0.9553817016317018</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01805025421338715</v>
+        <v>0.007934334836083086</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9695691534081627</v>
+        <v>0.9146855105678636</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01907251128167408</v>
+        <v>0.01456043433314883</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9243243243243244</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03783783783783785</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.9480 ± 0.0163</t>
+          <t>0.9586 ± 0.0077</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.9457 ± 0.0181</t>
+          <t>0.9554 ± 0.0079</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.9696 ± 0.0191</t>
+          <t>0.9147 ± 0.0146</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.9243 ± 0.0378</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GradientBoost</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9453333333333334</v>
+        <v>0.9571428571428571</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02186829262247564</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9434358295745456</v>
+        <v>0.9538461538461538</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02290830453192941</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9621073821073821</v>
+        <v>0.9117647058823529</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03145211250564695</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.927027027027027</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03831742399664279</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.9453 ± 0.0219</t>
+          <t>0.9571 ± 0.0000</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.9434 ± 0.0229</t>
+          <t>0.9538 ± 0.0000</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.9621 ± 0.0315</t>
+          <t>0.9118 ± 0.0000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.9270 ± 0.0383</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
     </row>
@@ -863,149 +863,149 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9386666666666666</v>
+        <v>0.9428571428571428</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02809507667427396</v>
+        <v>0.01106566670344977</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9368746605327736</v>
+        <v>0.9379673104673104</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0301395105853278</v>
+        <v>0.01258359015036446</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9485001062672286</v>
+        <v>0.9019757448433919</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03246548163303751</v>
+        <v>0.01157231801869656</v>
       </c>
       <c r="H9" t="n">
-        <v>0.927027027027027</v>
+        <v>0.9774193548387098</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04530555301146002</v>
+        <v>0.02519435379324729</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.9387 ± 0.0281</t>
+          <t>0.9429 ± 0.0111</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.9369 ± 0.0301</t>
+          <t>0.9380 ± 0.0126</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.9485 ± 0.0325</t>
+          <t>0.9020 ± 0.0116</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.9270 ± 0.0453</t>
+          <t>0.9774 ± 0.0252</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.916</v>
+        <v>0.9328571428571429</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02924228293261507</v>
+        <v>0.009147320339189774</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9106235622271077</v>
+        <v>0.9291236127057022</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03519628885402667</v>
+        <v>0.009571073413954689</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9512569712569713</v>
+        <v>0.8726797385620916</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04457152412772801</v>
+        <v>0.01244948101449847</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8783783783783784</v>
+        <v>0.9935483870967744</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06756756756756757</v>
+        <v>0.0129032258064516</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.9160 ± 0.0292</t>
+          <t>0.9329 ± 0.0091</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.9106 ± 0.0352</t>
+          <t>0.9291 ± 0.0096</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.9513 ± 0.0446</t>
+          <t>0.8727 ± 0.0124</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.8784 ± 0.0676</t>
+          <t>0.9935 ± 0.0129</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.9142857142857143</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04580150409951377</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9091850229600009</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="E11" t="n">
-        <v>0.04235604543369281</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.889508683313031</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06924353342860282</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9324324324324325</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02769446152962055</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.9067 ± 0.0458</t>
+          <t>0.9143 ± 0.0000</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.9092 ± 0.0424</t>
+          <t>0.8929 ± 0.0000</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.8895 ± 0.0692</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.9324 ± 0.0277</t>
+          <t>0.8065 ± 0.0000</t>
         </is>
       </c>
     </row>
@@ -1178,108 +1178,108 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SVM-RBF</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9573333333333333</v>
+        <v>0.9857142857142858</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01959591794226543</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9549442804586885</v>
+        <v>0.984126984126984</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02156270877056382</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9886418351124234</v>
+        <v>0.96875</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01392151593083359</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9243243243243244</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03783783783783785</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.9573 ± 0.0196</t>
+          <t>0.9857 ± 0.0000</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.9549 ± 0.0216</t>
+          <t>0.9841 ± 0.0000</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.9886 ± 0.0139</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.9243 ± 0.0378</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.5186666666666667</v>
+        <v>0.5571428571428572</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03975480404233486</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1652858413018168</v>
+        <v>0.5507246376811594</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.08803906963005416</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6571581196581197</v>
+        <v>0.5</v>
       </c>
       <c r="S2" t="n">
-        <v>0.239772939722718</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1</v>
+        <v>0.6129032258064517</v>
       </c>
       <c r="U2" t="n">
-        <v>0.05675675675675676</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.5187 ± 0.0398</t>
+          <t>0.5571 ± 0.0000</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.1653 ± 0.0880</t>
+          <t>0.5507 ± 0.0000</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.6572 ± 0.2398</t>
+          <t>0.5000 ± 0.0000</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.1000 ± 0.0568</t>
+          <t>0.6129 ± 0.0000</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>0.4386666666666665</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.7896584391568717</v>
+        <v>0.4334023464458245</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3314837154543038</v>
+        <v>0.46875</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8243243243243245</v>
+        <v>0.3870967741935483</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -1290,108 +1290,108 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM-RBF</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9559999999999998</v>
+        <v>0.9857142857142858</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02235073948565364</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9533200486764233</v>
+        <v>0.984126984126984</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02507909177402514</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9886418351124234</v>
+        <v>0.96875</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01392151593083359</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9216216216216218</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04432762018069385</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.9560 ± 0.0224</t>
+          <t>0.9857 ± 0.0000</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.9533 ± 0.0251</t>
+          <t>0.9841 ± 0.0000</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.9886 ± 0.0139</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.9216 ± 0.0443</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.5200000000000001</v>
+        <v>0.5571428571428572</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03955305859784353</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1648229171579141</v>
+        <v>0.5507246376811594</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.09403041091051378</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6543803418803419</v>
+        <v>0.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2492735674639203</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1</v>
+        <v>0.6129032258064517</v>
       </c>
       <c r="U3" t="n">
-        <v>0.06049467374486323</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.5200 ± 0.0396</t>
+          <t>0.5571 ± 0.0000</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.1648 ± 0.0940</t>
+          <t>0.5507 ± 0.0000</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.6544 ± 0.2493</t>
+          <t>0.5000 ± 0.0000</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.1000 ± 0.0605</t>
+          <t>0.6129 ± 0.0000</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>0.4359999999999997</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.7884971315185092</v>
+        <v>0.4334023464458245</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3342614932320815</v>
+        <v>0.46875</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8216216216216218</v>
+        <v>0.3870967741935483</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
@@ -1402,108 +1402,108 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9546666666666667</v>
+        <v>0.9771428571428572</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0170749979664876</v>
+        <v>0.006998542122237681</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9526820073843034</v>
+        <v>0.9749007936507936</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01853939000672906</v>
+        <v>0.007533152978797446</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9775705964096056</v>
+        <v>0.9511363636363637</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01630136615858147</v>
+        <v>0.01438147386861333</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9297297297297298</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03243243243243243</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.9547 ± 0.0171</t>
+          <t>0.9771 ± 0.0070</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.9527 ± 0.0185</t>
+          <t>0.9749 ± 0.0075</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.9776 ± 0.0163</t>
+          <t>0.9511 ± 0.0144</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.9297 ± 0.0324</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.5693333333333334</v>
+        <v>0.4357142857142858</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03957552554574888</v>
+        <v>0.03899241161130336</v>
       </c>
       <c r="P4" t="n">
-        <v>0.281880441520921</v>
+        <v>0.3326640232531992</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1272531044224129</v>
+        <v>0.05897776290659064</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8423852813852812</v>
+        <v>0.3477625399360661</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1718049744661832</v>
+        <v>0.05577213585322661</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1837837837837838</v>
+        <v>0.3193548387096775</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1024178125486293</v>
+        <v>0.0619657184267695</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.5693 ± 0.0396</t>
+          <t>0.4357 ± 0.0390</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.2819 ± 0.1273</t>
+          <t>0.3327 ± 0.0590</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.8424 ± 0.1718</t>
+          <t>0.3478 ± 0.0558</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.1838 ± 0.1024</t>
+          <t>0.3194 ± 0.0620</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>0.3853333333333333</v>
+        <v>0.5414285714285714</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.6708015658633824</v>
+        <v>0.6422367703975944</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1351853150243244</v>
+        <v>0.6033738237002976</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.745945945945946</v>
+        <v>0.6806451612903226</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
@@ -1514,108 +1514,108 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9533333333333331</v>
+        <v>0.9714285714285713</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01366260102127946</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9513798805474434</v>
+        <v>0.96875</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01493412066788913</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9752040740430834</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01902222469328762</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9297297297297298</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03243243243243243</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.9533 ± 0.0137</t>
+          <t>0.9714 ± 0.0000</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.9514 ± 0.0149</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.9752 ± 0.0190</t>
+          <t>0.9394 ± 0.0000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.9297 ± 0.0324</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.5373333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04260412082312123</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4338927624648122</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06325484813902747</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5459838648962071</v>
+        <v>0.4307692307692308</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06521458701907638</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3621621621621622</v>
+        <v>0.9032258064516128</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0664227336618622</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.5373 ± 0.0426</t>
+          <t>0.4286 ± 0.0000</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4339 ± 0.0633</t>
+          <t>0.5833 ± 0.0000</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.5460 ± 0.0652</t>
+          <t>0.4308 ± 0.0000</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.3622 ± 0.0664</t>
+          <t>0.9032 ± 0.0000</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>0.4159999999999998</v>
+        <v>0.5428571428571427</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.5174871180826313</v>
+        <v>0.3854166666666667</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4292202091468763</v>
+        <v>0.5086247086247087</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.5675675675675675</v>
+        <v>0.09677419354838723</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -1626,108 +1626,108 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>GradientBoost</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9493333333333334</v>
+        <v>0.9714285714285713</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0258542925728871</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9471443985093639</v>
+        <v>0.96875</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02807031046294366</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9674413598097809</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02864768705787136</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9297297297297298</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05012766754322002</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.9493 ± 0.0259</t>
+          <t>0.9714 ± 0.0000</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.9471 ± 0.0281</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.9674 ± 0.0286</t>
+          <t>0.9394 ± 0.0000</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.9297 ± 0.0501</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.588</v>
+        <v>0.5428571428571428</v>
       </c>
       <c r="O6" t="n">
-        <v>0.07807688518377254</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4952854919834154</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.09531935715656055</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6319471563295094</v>
+        <v>0.4827586206896551</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1346701238878538</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4108108108108108</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="U6" t="n">
-        <v>0.08529585858410541</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.5880 ± 0.0781</t>
+          <t>0.5429 ± 0.0000</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.4953 ± 0.0953</t>
+          <t>0.4667 ± 0.0000</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.6319 ± 0.1347</t>
+          <t>0.4828 ± 0.0000</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.4108 ± 0.0853</t>
+          <t>0.4516 ± 0.0000</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>0.3613333333333334</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.4518589065259485</v>
+        <v>0.5020833333333333</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3354942034802715</v>
+        <v>0.4566353187042843</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.5189189189189189</v>
+        <v>0.5483870967741936</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1742,104 +1742,104 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9479999999999998</v>
+        <v>0.9585714285714285</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01627540748764492</v>
+        <v>0.007693092581620716</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9457327984769963</v>
+        <v>0.9553817016317018</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01805025421338715</v>
+        <v>0.007934334836083086</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9695691534081627</v>
+        <v>0.9146855105678636</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01907251128167408</v>
+        <v>0.01456043433314883</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9243243243243244</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03783783783783785</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.9480 ± 0.0163</t>
+          <t>0.9586 ± 0.0077</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.9457 ± 0.0181</t>
+          <t>0.9554 ± 0.0079</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.9696 ± 0.0191</t>
+          <t>0.9147 ± 0.0146</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.9243 ± 0.0378</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0.5213333333333334</v>
+        <v>0.4428571428571428</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06598316283551263</v>
+        <v>0.03670066451047179</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4142813933258118</v>
+        <v>0.3195982802137768</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.09950847439886906</v>
+        <v>0.04718203797953666</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5159377172535067</v>
+        <v>0.3482867467365219</v>
       </c>
       <c r="S7" t="n">
-        <v>0.09870162951692731</v>
+        <v>0.04606035697463466</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3486486486486486</v>
+        <v>0.2967741935483871</v>
       </c>
       <c r="U7" t="n">
-        <v>0.09703417876224996</v>
+        <v>0.05161290322580646</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.5213 ± 0.0660</t>
+          <t>0.4429 ± 0.0367</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.4143 ± 0.0995</t>
+          <t>0.3196 ± 0.0472</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.5159 ± 0.0987</t>
+          <t>0.3483 ± 0.0461</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.3486 ± 0.0970</t>
+          <t>0.2968 ± 0.0516</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>0.4266666666666664</v>
+        <v>0.5157142857142858</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5314514051511845</v>
+        <v>0.635783421417925</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.4536314361546561</v>
+        <v>0.5663987638313417</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.5756756756756758</v>
+        <v>0.7032258064516129</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1850,108 +1850,108 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GradientBoost</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9453333333333334</v>
+        <v>0.9571428571428571</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02186829262247564</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9434358295745456</v>
+        <v>0.9538461538461538</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02290830453192941</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9621073821073821</v>
+        <v>0.9117647058823529</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03145211250564695</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.927027027027027</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03831742399664279</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.9453 ± 0.0219</t>
+          <t>0.9571 ± 0.0000</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.9434 ± 0.0229</t>
+          <t>0.9538 ± 0.0000</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.9621 ± 0.0315</t>
+          <t>0.9118 ± 0.0000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.9270 ± 0.0383</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.5693333333333334</v>
+        <v>0.5285714285714286</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03820413008505175</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4665383026983773</v>
+        <v>0.4590163934426229</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.06688598596345967</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5976570423041011</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="S8" t="n">
-        <v>0.05875270115468078</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3864864864864865</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="U8" t="n">
-        <v>0.07357112210170919</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.5693 ± 0.0382</t>
+          <t>0.5286 ± 0.0000</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.4665 ± 0.0669</t>
+          <t>0.4590 ± 0.0000</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.5977 ± 0.0588</t>
+          <t>0.4667 ± 0.0000</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.3865 ± 0.0736</t>
+          <t>0.4516 ± 0.0000</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>0.376</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.4768975268761684</v>
+        <v>0.4948297604035309</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.364450339803281</v>
+        <v>0.4450980392156862</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.5405405405405406</v>
+        <v>0.5483870967741936</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -1966,104 +1966,104 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9386666666666666</v>
+        <v>0.9428571428571428</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02809507667427396</v>
+        <v>0.01106566670344977</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9368746605327736</v>
+        <v>0.9379673104673104</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0301395105853278</v>
+        <v>0.01258359015036446</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9485001062672286</v>
+        <v>0.9019757448433919</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03246548163303751</v>
+        <v>0.01157231801869656</v>
       </c>
       <c r="H9" t="n">
-        <v>0.927027027027027</v>
+        <v>0.9774193548387098</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04530555301146002</v>
+        <v>0.02519435379324729</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.9387 ± 0.0281</t>
+          <t>0.9429 ± 0.0111</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.9369 ± 0.0301</t>
+          <t>0.9380 ± 0.0126</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.9485 ± 0.0325</t>
+          <t>0.9020 ± 0.0116</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.9270 ± 0.0453</t>
+          <t>0.9774 ± 0.0252</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4542857142857143</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05198290317231447</v>
+        <v>0.02373321103690879</v>
       </c>
       <c r="P9" t="n">
-        <v>0.381188188267436</v>
+        <v>0.3288815459430735</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.06749667957709082</v>
+        <v>0.04181276949365909</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4459420829741657</v>
+        <v>0.360034188034188</v>
       </c>
       <c r="S9" t="n">
-        <v>0.07442553174320657</v>
+        <v>0.03692765966425206</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3351351351351352</v>
+        <v>0.3032258064516129</v>
       </c>
       <c r="U9" t="n">
-        <v>0.06858690562405147</v>
+        <v>0.04607373179705065</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.4667 ± 0.0520</t>
+          <t>0.4543 ± 0.0237</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.3812 ± 0.0675</t>
+          <t>0.3289 ± 0.0418</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.4459 ± 0.0744</t>
+          <t>0.3600 ± 0.0369</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.3351 ± 0.0686</t>
+          <t>0.3032 ± 0.0461</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>0.472</v>
+        <v>0.4885714285714285</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.5556864722653376</v>
+        <v>0.6090857645242369</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.5025580232930629</v>
+        <v>0.541941556809204</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.5918918918918918</v>
+        <v>0.6741935483870969</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -2074,108 +2074,108 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.916</v>
+        <v>0.9328571428571429</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02924228293261507</v>
+        <v>0.009147320339189774</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9106235622271077</v>
+        <v>0.9291236127057022</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03519628885402667</v>
+        <v>0.009571073413954689</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9512569712569713</v>
+        <v>0.8726797385620916</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04457152412772801</v>
+        <v>0.01244948101449847</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8783783783783784</v>
+        <v>0.9935483870967744</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06756756756756757</v>
+        <v>0.0129032258064516</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.9160 ± 0.0292</t>
+          <t>0.9329 ± 0.0091</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.9106 ± 0.0352</t>
+          <t>0.9291 ± 0.0096</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.9513 ± 0.0446</t>
+          <t>0.8727 ± 0.0124</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.8784 ± 0.0676</t>
+          <t>0.9935 ± 0.0129</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0.5200000000000001</v>
+        <v>0.5157142857142857</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04216370213557839</v>
+        <v>0.02065261756400137</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4672312094126575</v>
+        <v>0.4543135675381752</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.04261969382271548</v>
+        <v>0.01379532248949963</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5185386059065147</v>
+        <v>0.4542118768328446</v>
       </c>
       <c r="S10" t="n">
-        <v>0.05039762825351469</v>
+        <v>0.02210798102124477</v>
       </c>
       <c r="T10" t="n">
-        <v>0.427027027027027</v>
+        <v>0.4548387096774193</v>
       </c>
       <c r="U10" t="n">
-        <v>0.04490066952928689</v>
+        <v>0.009677419354838717</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.5200 ± 0.0422</t>
+          <t>0.5157 ± 0.0207</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.4672 ± 0.0426</t>
+          <t>0.4543 ± 0.0138</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.5185 ± 0.0504</t>
+          <t>0.4542 ± 0.0221</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.4270 ± 0.0449</t>
+          <t>0.4548 ± 0.0097</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>0.3959999999999999</v>
+        <v>0.4171428571428573</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.4433923528144502</v>
+        <v>0.474810045167527</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.4327183653504566</v>
+        <v>0.4184678617292469</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.4513513513513514</v>
+        <v>0.5387096774193552</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -2186,108 +2186,108 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.9142857142857143</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04580150409951377</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9091850229600009</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="E11" t="n">
-        <v>0.04235604543369281</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.889508683313031</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06924353342860282</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9324324324324325</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02769446152962055</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.9067 ± 0.0458</t>
+          <t>0.9143 ± 0.0000</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.9092 ± 0.0424</t>
+          <t>0.8929 ± 0.0000</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.8895 ± 0.0692</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.9324 ± 0.0277</t>
+          <t>0.8065 ± 0.0000</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0.5093333333333333</v>
+        <v>0.4142857142857143</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02133333333333333</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4917474116830446</v>
+        <v>0.2545454545454545</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.04548098950173056</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5019145190771878</v>
+        <v>0.2916666666666666</v>
       </c>
       <c r="S11" t="n">
-        <v>0.021382753854929</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4864864864864865</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="U11" t="n">
-        <v>0.07644397634449161</v>
+        <v>2.775557561562891e-17</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.5093 ± 0.0213</t>
+          <t>0.4143 ± 0.0000</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.4917 ± 0.0455</t>
+          <t>0.2545 ± 0.0000</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.5019 ± 0.0214</t>
+          <t>0.2917 ± 0.0000</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.4865 ± 0.0764</t>
+          <t>0.2258 ± 0.0000</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>0.3973333333333333</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.4174376112769563</v>
+        <v>0.6383116883116884</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.3875941642358433</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.4459459459459459</v>
+        <v>0.5806451612903225</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2298,95 +2298,95 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SVM-RBF</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9573333333333333</v>
+        <v>0.9857142857142858</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01959591794226543</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9549442804586885</v>
+        <v>0.984126984126984</v>
       </c>
       <c r="E12" t="n">
-        <v>0.02156270877056382</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9886418351124234</v>
+        <v>0.96875</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01392151593083359</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9243243243243244</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0.03783783783783785</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.9573 ± 0.0196</t>
+          <t>0.9857 ± 0.0000</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.9549 ± 0.0216</t>
+          <t>0.9841 ± 0.0000</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.9886 ± 0.0139</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.9243 ± 0.0378</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0.9573333333333333</v>
+        <v>0.9857142857142858</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01959591794226543</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9549442804586885</v>
+        <v>0.984126984126984</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.02156270877056382</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9886418351124234</v>
+        <v>0.96875</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01392151593083359</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9243243243243244</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0.03783783783783785</v>
+        <v>0</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.9573 ± 0.0196</t>
+          <t>0.9857 ± 0.0000</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.9549 ± 0.0216</t>
+          <t>0.9841 ± 0.0000</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>0.9886 ± 0.0139</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>0.9243 ± 0.0378</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="Z12" t="n">
@@ -2410,108 +2410,108 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM-RBF</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9559999999999998</v>
+        <v>0.9857142857142858</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02235073948565364</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9533200486764233</v>
+        <v>0.984126984126984</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02507909177402514</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9886418351124234</v>
+        <v>0.96875</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01392151593083359</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9216216216216218</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.04432762018069385</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.9560 ± 0.0224</t>
+          <t>0.9857 ± 0.0000</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.9533 ± 0.0251</t>
+          <t>0.9841 ± 0.0000</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.9886 ± 0.0139</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0.9216 ± 0.0443</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.9573333333333333</v>
+        <v>0.9857142857142858</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01959591794226543</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9549442804586885</v>
+        <v>0.984126984126984</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.02156270877056382</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9886418351124234</v>
+        <v>0.96875</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01392151593083359</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9243243243243244</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.03783783783783785</v>
+        <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>0.9573 ± 0.0196</t>
+          <t>0.9857 ± 0.0000</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.9549 ± 0.0216</t>
+          <t>0.9841 ± 0.0000</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>0.9886 ± 0.0139</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>0.9243 ± 0.0378</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>-0.001333333333333409</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.001624231782265229</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.002702702702702675</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2522,105 +2522,105 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9546666666666667</v>
+        <v>0.9771428571428572</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0170749979664876</v>
+        <v>0.006998542122237681</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9526820073843034</v>
+        <v>0.9749007936507936</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01853939000672906</v>
+        <v>0.007533152978797446</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9775705964096056</v>
+        <v>0.9511363636363637</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01630136615858147</v>
+        <v>0.01438147386861333</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9297297297297298</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.03243243243243243</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.9547 ± 0.0171</t>
+          <t>0.9771 ± 0.0070</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.9527 ± 0.0185</t>
+          <t>0.9749 ± 0.0075</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.9776 ± 0.0163</t>
+          <t>0.9511 ± 0.0144</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.9297 ± 0.0324</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0.9506666666666668</v>
+        <v>0.9571428571428571</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01982142499642468</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9488340101644223</v>
+        <v>0.9538461538461538</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.02099408233403052</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9696699246699246</v>
+        <v>0.9117647058823529</v>
       </c>
       <c r="S14" t="n">
-        <v>0.02511257901514386</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9297297297297298</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0.03243243243243243</v>
+        <v>0</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.9507 ± 0.0198</t>
+          <t>0.9571 ± 0.0000</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.9488 ± 0.0210</t>
+          <t>0.9538 ± 0.0000</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0.9697 ± 0.0251</t>
+          <t>0.9118 ± 0.0000</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>0.9297 ± 0.0324</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>0.003999999999999893</v>
+        <v>0.02000000000000013</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.003847997219881161</v>
+        <v>0.02105463980463984</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.007900671739681009</v>
+        <v>0.03937165775401075</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2634,108 +2634,108 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9533333333333331</v>
+        <v>0.9714285714285713</v>
       </c>
       <c r="C15" t="n">
-        <v>0.01366260102127946</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9513798805474434</v>
+        <v>0.96875</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01493412066788913</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9752040740430834</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01902222469328762</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9297297297297298</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0.03243243243243243</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.9533 ± 0.0137</t>
+          <t>0.9714 ± 0.0000</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.9514 ± 0.0149</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.9752 ± 0.0190</t>
+          <t>0.9394 ± 0.0000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.9297 ± 0.0324</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0.9613333333333334</v>
+        <v>0.9714285714285713</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01833030277982337</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9593753143373979</v>
+        <v>0.96875</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.01982438504397334</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9887212001917887</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="S15" t="n">
-        <v>0.01382508701882397</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9324324324324325</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03471684480720305</v>
+        <v>0</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.9613 ± 0.0183</t>
+          <t>0.9714 ± 0.0000</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.9594 ± 0.0198</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>0.9887 ± 0.0138</t>
+          <t>0.9394 ± 0.0000</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>0.9324 ± 0.0347</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>-0.008000000000000229</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.007995433789954487</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.01351712614870526</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.002702702702702675</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2746,108 +2746,108 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>GradientBoost</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9493333333333334</v>
+        <v>0.9714285714285713</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0258542925728871</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9471443985093639</v>
+        <v>0.96875</v>
       </c>
       <c r="E16" t="n">
-        <v>0.02807031046294366</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9674413598097809</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="G16" t="n">
-        <v>0.02864768705787136</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9297297297297298</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0.05012766754322002</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.9493 ± 0.0259</t>
+          <t>0.9714 ± 0.0000</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.9471 ± 0.0281</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.9674 ± 0.0286</t>
+          <t>0.9394 ± 0.0000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.9297 ± 0.0501</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0.9613333333333334</v>
+        <v>0.9571428571428571</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01392040867854741</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9597232349628644</v>
+        <v>0.9538461538461538</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.01496877976938839</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9835374073764166</v>
+        <v>0.9117647058823529</v>
       </c>
       <c r="S16" t="n">
-        <v>0.01788472955671827</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9378378378378379</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0.02972972972972974</v>
+        <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0.9613 ± 0.0139</t>
+          <t>0.9571 ± 0.0000</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.9597 ± 0.0150</t>
+          <t>0.9538 ± 0.0000</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>0.9835 ± 0.0179</t>
+          <t>0.9118 ± 0.0000</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>0.9378 ± 0.0297</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>-0.01200000000000001</v>
+        <v>0.01428571428571423</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.01257883645350044</v>
+        <v>0.01490384615384621</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.01609604756663574</v>
+        <v>0.02762923351158653</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.008108108108108136</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2862,104 +2862,104 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9479999999999998</v>
+        <v>0.9585714285714285</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01627540748764492</v>
+        <v>0.007693092581620716</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9457327984769963</v>
+        <v>0.9553817016317018</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01805025421338715</v>
+        <v>0.007934334836083086</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9695691534081627</v>
+        <v>0.9146855105678636</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01907251128167408</v>
+        <v>0.01456043433314883</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9243243243243244</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0.03783783783783785</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.9480 ± 0.0163</t>
+          <t>0.9586 ± 0.0077</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.9457 ± 0.0181</t>
+          <t>0.9554 ± 0.0079</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.9696 ± 0.0191</t>
+          <t>0.9147 ± 0.0146</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.9243 ± 0.0378</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0.9653333333333333</v>
+        <v>0.9671428571428571</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01359738536958078</v>
+        <v>0.009147320339189774</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9639988000734674</v>
+        <v>0.96432615995116</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.01427518868765128</v>
+        <v>0.009639743532762493</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9860274560274561</v>
+        <v>0.9312778520499109</v>
       </c>
       <c r="S17" t="n">
-        <v>0.01397856672567184</v>
+        <v>0.01804596280141018</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9432432432432434</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0.02245033476464344</v>
+        <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.9653 ± 0.0136</t>
+          <t>0.9671 ± 0.0091</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.9640 ± 0.0143</t>
+          <t>0.9643 ± 0.0096</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>0.9860 ± 0.0140</t>
+          <t>0.9313 ± 0.0180</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>0.9432 ± 0.0225</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>-0.01733333333333342</v>
+        <v>-0.008571428571428563</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.01826600159647107</v>
+        <v>-0.008944458319458226</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.01645830261929337</v>
+        <v>-0.01659234148204725</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.01891891891891895</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2970,108 +2970,108 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GradientBoost</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9453333333333334</v>
+        <v>0.9571428571428571</v>
       </c>
       <c r="C18" t="n">
-        <v>0.02186829262247564</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9434358295745456</v>
+        <v>0.9538461538461538</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02290830453192941</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9621073821073821</v>
+        <v>0.9117647058823529</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03145211250564695</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.927027027027027</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.03831742399664279</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.9453 ± 0.0219</t>
+          <t>0.9571 ± 0.0000</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.9434 ± 0.0229</t>
+          <t>0.9538 ± 0.0000</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.9621 ± 0.0315</t>
+          <t>0.9118 ± 0.0000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.9270 ± 0.0383</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0.9613333333333334</v>
+        <v>0.9571428571428571</v>
       </c>
       <c r="O18" t="n">
-        <v>0.01733333333333335</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9594184718330967</v>
+        <v>0.9538461538461538</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.01859936423559992</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9887212001917887</v>
+        <v>0.9117647058823529</v>
       </c>
       <c r="S18" t="n">
-        <v>0.01382508701882397</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9324324324324325</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0.03254485021295216</v>
+        <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.9613 ± 0.0173</t>
+          <t>0.9571 ± 0.0000</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.9594 ± 0.0186</t>
+          <t>0.9538 ± 0.0000</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>0.9887 ± 0.0138</t>
+          <t>0.9118 ± 0.0000</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>0.9324 ± 0.0325</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>-0.01600000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0.01598264225855106</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.02661381808440655</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.005405405405405461</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3086,104 +3086,104 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9386666666666666</v>
+        <v>0.9428571428571428</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02809507667427396</v>
+        <v>0.01106566670344977</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9368746605327736</v>
+        <v>0.9379673104673104</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0301395105853278</v>
+        <v>0.01258359015036446</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9485001062672286</v>
+        <v>0.9019757448433919</v>
       </c>
       <c r="G19" t="n">
-        <v>0.03246548163303751</v>
+        <v>0.01157231801869656</v>
       </c>
       <c r="H19" t="n">
-        <v>0.927027027027027</v>
+        <v>0.9774193548387098</v>
       </c>
       <c r="I19" t="n">
-        <v>0.04530555301146002</v>
+        <v>0.02519435379324729</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.9387 ± 0.0281</t>
+          <t>0.9429 ± 0.0111</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.9369 ± 0.0301</t>
+          <t>0.9380 ± 0.0126</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.9485 ± 0.0325</t>
+          <t>0.9020 ± 0.0116</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.9270 ± 0.0453</t>
+          <t>0.9774 ± 0.0252</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0.9626666666666667</v>
+        <v>0.9342857142857144</v>
       </c>
       <c r="O19" t="n">
-        <v>0.02048305532764963</v>
+        <v>0.01829464067837958</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9614029655741019</v>
+        <v>0.9291201050574693</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.02119837818684929</v>
+        <v>0.01897011088793063</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9781359532907519</v>
+        <v>0.8920485144204309</v>
       </c>
       <c r="S19" t="n">
-        <v>0.02363022285354803</v>
+        <v>0.03259370079531765</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9459459459459459</v>
+        <v>0.9709677419354839</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0319788096383763</v>
+        <v>0.0304321972001826</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.9627 ± 0.0205</t>
+          <t>0.9343 ± 0.0183</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.9614 ± 0.0212</t>
+          <t>0.9291 ± 0.0190</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>0.9781 ± 0.0236</t>
+          <t>0.8920 ± 0.0326</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>0.9459 ± 0.0320</t>
+          <t>0.9710 ± 0.0304</t>
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>-0.02400000000000002</v>
+        <v>0.008571428571428452</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.0245283050413283</v>
+        <v>0.008847205409841075</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.02963584702352329</v>
+        <v>0.009927230422961064</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.01891891891891895</v>
+        <v>0.006451612903225934</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3194,108 +3194,108 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.916</v>
+        <v>0.9328571428571429</v>
       </c>
       <c r="C20" t="n">
-        <v>0.02924228293261507</v>
+        <v>0.009147320339189774</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9106235622271077</v>
+        <v>0.9291236127057022</v>
       </c>
       <c r="E20" t="n">
-        <v>0.03519628885402667</v>
+        <v>0.009571073413954689</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9512569712569713</v>
+        <v>0.8726797385620916</v>
       </c>
       <c r="G20" t="n">
-        <v>0.04457152412772801</v>
+        <v>0.01244948101449847</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8783783783783784</v>
+        <v>0.9935483870967744</v>
       </c>
       <c r="I20" t="n">
-        <v>0.06756756756756757</v>
+        <v>0.0129032258064516</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.9160 ± 0.0292</t>
+          <t>0.9329 ± 0.0091</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.9106 ± 0.0352</t>
+          <t>0.9291 ± 0.0096</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.9513 ± 0.0446</t>
+          <t>0.8727 ± 0.0124</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.8784 ± 0.0676</t>
+          <t>0.9935 ± 0.0129</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.8785714285714287</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0304046780026437</v>
+        <v>0.02575393768188564</v>
       </c>
       <c r="P20" t="n">
-        <v>0.942560698600406</v>
+        <v>0.8800095564745828</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.03419752504743662</v>
+        <v>0.0225762954145012</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9881840449582384</v>
+        <v>0.7864589646885076</v>
       </c>
       <c r="S20" t="n">
-        <v>0.01452403234957743</v>
+        <v>0.03620129452112127</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9027027027027028</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0582179979149676</v>
+        <v>0</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.9467 ± 0.0304</t>
+          <t>0.8786 ± 0.0258</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.9426 ± 0.0342</t>
+          <t>0.8800 ± 0.0226</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>0.9882 ± 0.0145</t>
+          <t>0.7865 ± 0.0362</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>0.9027 ± 0.0582</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>-0.03066666666666662</v>
+        <v>0.05428571428571427</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.03193713637329831</v>
+        <v>0.04911405623111942</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.03692707370126713</v>
+        <v>0.08622077387358396</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.02432432432432441</v>
+        <v>-0.006451612903225601</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3306,108 +3306,108 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.9142857142857143</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04580150409951377</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9091850229600009</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="E21" t="n">
-        <v>0.04235604543369281</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.889508683313031</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.06924353342860282</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9324324324324325</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="I21" t="n">
-        <v>0.02769446152962055</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.9067 ± 0.0458</t>
+          <t>0.9143 ± 0.0000</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.9092 ± 0.0424</t>
+          <t>0.8929 ± 0.0000</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.8895 ± 0.0692</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.9324 ± 0.0277</t>
+          <t>0.8065 ± 0.0000</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0.9186666666666667</v>
+        <v>0.8714285714285716</v>
       </c>
       <c r="O21" t="n">
-        <v>0.02490872225635921</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9170030677621485</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.02635851876379843</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9219388885874954</v>
+        <v>0.84375</v>
       </c>
       <c r="S21" t="n">
-        <v>0.03039795167188453</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9135135135135135</v>
+        <v>0.8709677419354838</v>
       </c>
       <c r="U21" t="n">
-        <v>0.04151970674523572</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.9187 ± 0.0249</t>
+          <t>0.8714 ± 0.0000</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.9170 ± 0.0264</t>
+          <t>0.8571 ± 0.0000</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.9219 ± 0.0304</t>
+          <t>0.8438 ± 0.0000</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.9135 ± 0.0415</t>
+          <t>0.8710 ± 0.0000</t>
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>-0.01200000000000012</v>
+        <v>0.0428571428571427</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.007818044802147539</v>
+        <v>0.03571428571428581</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.03243020527446439</v>
+        <v>0.15625</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.01891891891891895</v>
+        <v>-0.06451612903225801</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -3463,16 +3463,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.0117333333333334</v>
+        <v>0.01314285714285712</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.01168826348776353</v>
+        <v>0.01206895749942741</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.01637777486786147</v>
+        <v>0.0302806554080095</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.006216216216216231</v>
+        <v>-0.006451612903225767</v>
       </c>
     </row>
     <row r="3">
@@ -3482,16 +3482,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4105333333333333</v>
+        <v>0.472</v>
       </c>
       <c r="C3" t="n">
-        <v>0.564316852953144</v>
+        <v>0.5249362143114151</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3706597265175157</v>
+        <v>0.5186373405948104</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6083783783783784</v>
+        <v>0.5145161290322581</v>
       </c>
     </row>
   </sheetData>
@@ -3663,108 +3663,108 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SVM-RBF</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9573333333333333</v>
+        <v>0.9857142857142858</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01959591794226543</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9549442804586885</v>
+        <v>0.984126984126984</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02156270877056382</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9886418351124234</v>
+        <v>0.96875</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01392151593083359</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9243243243243244</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03783783783783785</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.9573 ± 0.0196</t>
+          <t>0.9857 ± 0.0000</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.9549 ± 0.0216</t>
+          <t>0.9841 ± 0.0000</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.9886 ± 0.0139</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.9243 ± 0.0378</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.5186666666666667</v>
+        <v>0.5571428571428572</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03975480404233486</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1652858413018168</v>
+        <v>0.5507246376811594</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.08803906963005416</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6571581196581197</v>
+        <v>0.5</v>
       </c>
       <c r="S2" t="n">
-        <v>0.239772939722718</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1</v>
+        <v>0.6129032258064517</v>
       </c>
       <c r="U2" t="n">
-        <v>0.05675675675675676</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.5187 ± 0.0398</t>
+          <t>0.5571 ± 0.0000</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.1653 ± 0.0880</t>
+          <t>0.5507 ± 0.0000</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.6572 ± 0.2398</t>
+          <t>0.5000 ± 0.0000</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.1000 ± 0.0568</t>
+          <t>0.6129 ± 0.0000</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>0.4386666666666665</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.7896584391568717</v>
+        <v>0.4334023464458245</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3314837154543038</v>
+        <v>0.46875</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8243243243243245</v>
+        <v>0.3870967741935483</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -3775,108 +3775,108 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM-RBF</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9559999999999998</v>
+        <v>0.9857142857142858</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02235073948565364</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9533200486764233</v>
+        <v>0.984126984126984</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02507909177402514</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9886418351124234</v>
+        <v>0.96875</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01392151593083359</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9216216216216218</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04432762018069385</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.9560 ± 0.0224</t>
+          <t>0.9857 ± 0.0000</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.9533 ± 0.0251</t>
+          <t>0.9841 ± 0.0000</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.9886 ± 0.0139</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.9216 ± 0.0443</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.5200000000000001</v>
+        <v>0.5571428571428572</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03955305859784353</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1648229171579141</v>
+        <v>0.5507246376811594</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.09403041091051378</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6543803418803419</v>
+        <v>0.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2492735674639203</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1</v>
+        <v>0.6129032258064517</v>
       </c>
       <c r="U3" t="n">
-        <v>0.06049467374486323</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.5200 ± 0.0396</t>
+          <t>0.5571 ± 0.0000</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.1648 ± 0.0940</t>
+          <t>0.5507 ± 0.0000</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.6544 ± 0.2493</t>
+          <t>0.5000 ± 0.0000</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.1000 ± 0.0605</t>
+          <t>0.6129 ± 0.0000</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>0.4359999999999997</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.7884971315185092</v>
+        <v>0.4334023464458245</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3342614932320815</v>
+        <v>0.46875</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8216216216216218</v>
+        <v>0.3870967741935483</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
@@ -3887,108 +3887,108 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9546666666666667</v>
+        <v>0.9771428571428572</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0170749979664876</v>
+        <v>0.006998542122237681</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9526820073843034</v>
+        <v>0.9749007936507936</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01853939000672906</v>
+        <v>0.007533152978797446</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9775705964096056</v>
+        <v>0.9511363636363637</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01630136615858147</v>
+        <v>0.01438147386861333</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9297297297297298</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03243243243243243</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.9547 ± 0.0171</t>
+          <t>0.9771 ± 0.0070</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.9527 ± 0.0185</t>
+          <t>0.9749 ± 0.0075</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.9776 ± 0.0163</t>
+          <t>0.9511 ± 0.0144</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.9297 ± 0.0324</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.5693333333333334</v>
+        <v>0.4357142857142858</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03957552554574888</v>
+        <v>0.03899241161130336</v>
       </c>
       <c r="P4" t="n">
-        <v>0.281880441520921</v>
+        <v>0.3326640232531992</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1272531044224129</v>
+        <v>0.05897776290659064</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8423852813852812</v>
+        <v>0.3477625399360661</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1718049744661832</v>
+        <v>0.05577213585322661</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1837837837837838</v>
+        <v>0.3193548387096775</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1024178125486293</v>
+        <v>0.0619657184267695</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.5693 ± 0.0396</t>
+          <t>0.4357 ± 0.0390</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.2819 ± 0.1273</t>
+          <t>0.3327 ± 0.0590</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.8424 ± 0.1718</t>
+          <t>0.3478 ± 0.0558</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.1838 ± 0.1024</t>
+          <t>0.3194 ± 0.0620</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>0.3853333333333333</v>
+        <v>0.5414285714285714</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.6708015658633824</v>
+        <v>0.6422367703975944</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1351853150243244</v>
+        <v>0.6033738237002976</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.745945945945946</v>
+        <v>0.6806451612903226</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
@@ -3999,108 +3999,108 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9533333333333331</v>
+        <v>0.9714285714285713</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01366260102127946</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9513798805474434</v>
+        <v>0.96875</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01493412066788913</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9752040740430834</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01902222469328762</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9297297297297298</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03243243243243243</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.9533 ± 0.0137</t>
+          <t>0.9714 ± 0.0000</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.9514 ± 0.0149</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.9752 ± 0.0190</t>
+          <t>0.9394 ± 0.0000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.9297 ± 0.0324</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.5373333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04260412082312123</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4338927624648122</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06325484813902747</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5459838648962071</v>
+        <v>0.4307692307692308</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06521458701907638</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3621621621621622</v>
+        <v>0.9032258064516128</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0664227336618622</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.5373 ± 0.0426</t>
+          <t>0.4286 ± 0.0000</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4339 ± 0.0633</t>
+          <t>0.5833 ± 0.0000</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.5460 ± 0.0652</t>
+          <t>0.4308 ± 0.0000</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.3622 ± 0.0664</t>
+          <t>0.9032 ± 0.0000</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>0.4159999999999998</v>
+        <v>0.5428571428571427</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.5174871180826313</v>
+        <v>0.3854166666666667</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4292202091468763</v>
+        <v>0.5086247086247087</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.5675675675675675</v>
+        <v>0.09677419354838723</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -4111,108 +4111,108 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>GradientBoost</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9493333333333334</v>
+        <v>0.9714285714285713</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0258542925728871</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9471443985093639</v>
+        <v>0.96875</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02807031046294366</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9674413598097809</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02864768705787136</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9297297297297298</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05012766754322002</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.9493 ± 0.0259</t>
+          <t>0.9714 ± 0.0000</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.9471 ± 0.0281</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.9674 ± 0.0286</t>
+          <t>0.9394 ± 0.0000</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.9297 ± 0.0501</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.588</v>
+        <v>0.5428571428571428</v>
       </c>
       <c r="O6" t="n">
-        <v>0.07807688518377254</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4952854919834154</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.09531935715656055</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6319471563295094</v>
+        <v>0.4827586206896551</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1346701238878538</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4108108108108108</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="U6" t="n">
-        <v>0.08529585858410541</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.5880 ± 0.0781</t>
+          <t>0.5429 ± 0.0000</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.4953 ± 0.0953</t>
+          <t>0.4667 ± 0.0000</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.6319 ± 0.1347</t>
+          <t>0.4828 ± 0.0000</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.4108 ± 0.0853</t>
+          <t>0.4516 ± 0.0000</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>0.3613333333333334</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.4518589065259485</v>
+        <v>0.5020833333333333</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3354942034802715</v>
+        <v>0.4566353187042843</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.5189189189189189</v>
+        <v>0.5483870967741936</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -4227,104 +4227,104 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9479999999999998</v>
+        <v>0.9585714285714285</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01627540748764492</v>
+        <v>0.007693092581620716</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9457327984769963</v>
+        <v>0.9553817016317018</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01805025421338715</v>
+        <v>0.007934334836083086</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9695691534081627</v>
+        <v>0.9146855105678636</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01907251128167408</v>
+        <v>0.01456043433314883</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9243243243243244</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03783783783783785</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.9480 ± 0.0163</t>
+          <t>0.9586 ± 0.0077</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.9457 ± 0.0181</t>
+          <t>0.9554 ± 0.0079</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.9696 ± 0.0191</t>
+          <t>0.9147 ± 0.0146</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.9243 ± 0.0378</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0.5213333333333334</v>
+        <v>0.4428571428571428</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06598316283551263</v>
+        <v>0.03670066451047179</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4142813933258118</v>
+        <v>0.3195982802137768</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.09950847439886906</v>
+        <v>0.04718203797953666</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5159377172535067</v>
+        <v>0.3482867467365219</v>
       </c>
       <c r="S7" t="n">
-        <v>0.09870162951692731</v>
+        <v>0.04606035697463466</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3486486486486486</v>
+        <v>0.2967741935483871</v>
       </c>
       <c r="U7" t="n">
-        <v>0.09703417876224996</v>
+        <v>0.05161290322580646</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.5213 ± 0.0660</t>
+          <t>0.4429 ± 0.0367</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.4143 ± 0.0995</t>
+          <t>0.3196 ± 0.0472</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.5159 ± 0.0987</t>
+          <t>0.3483 ± 0.0461</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.3486 ± 0.0970</t>
+          <t>0.2968 ± 0.0516</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>0.4266666666666664</v>
+        <v>0.5157142857142858</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5314514051511845</v>
+        <v>0.635783421417925</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.4536314361546561</v>
+        <v>0.5663987638313417</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.5756756756756758</v>
+        <v>0.7032258064516129</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -4335,108 +4335,108 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GradientBoost</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9453333333333334</v>
+        <v>0.9571428571428571</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02186829262247564</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9434358295745456</v>
+        <v>0.9538461538461538</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02290830453192941</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9621073821073821</v>
+        <v>0.9117647058823529</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03145211250564695</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.927027027027027</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03831742399664279</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.9453 ± 0.0219</t>
+          <t>0.9571 ± 0.0000</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.9434 ± 0.0229</t>
+          <t>0.9538 ± 0.0000</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.9621 ± 0.0315</t>
+          <t>0.9118 ± 0.0000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.9270 ± 0.0383</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.5693333333333334</v>
+        <v>0.5285714285714286</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03820413008505175</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4665383026983773</v>
+        <v>0.4590163934426229</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.06688598596345967</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5976570423041011</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="S8" t="n">
-        <v>0.05875270115468078</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3864864864864865</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="U8" t="n">
-        <v>0.07357112210170919</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.5693 ± 0.0382</t>
+          <t>0.5286 ± 0.0000</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.4665 ± 0.0669</t>
+          <t>0.4590 ± 0.0000</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.5977 ± 0.0588</t>
+          <t>0.4667 ± 0.0000</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.3865 ± 0.0736</t>
+          <t>0.4516 ± 0.0000</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>0.376</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.4768975268761684</v>
+        <v>0.4948297604035309</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.364450339803281</v>
+        <v>0.4450980392156862</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.5405405405405406</v>
+        <v>0.5483870967741936</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -4451,104 +4451,104 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9386666666666666</v>
+        <v>0.9428571428571428</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02809507667427396</v>
+        <v>0.01106566670344977</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9368746605327736</v>
+        <v>0.9379673104673104</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0301395105853278</v>
+        <v>0.01258359015036446</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9485001062672286</v>
+        <v>0.9019757448433919</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03246548163303751</v>
+        <v>0.01157231801869656</v>
       </c>
       <c r="H9" t="n">
-        <v>0.927027027027027</v>
+        <v>0.9774193548387098</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04530555301146002</v>
+        <v>0.02519435379324729</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.9387 ± 0.0281</t>
+          <t>0.9429 ± 0.0111</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.9369 ± 0.0301</t>
+          <t>0.9380 ± 0.0126</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.9485 ± 0.0325</t>
+          <t>0.9020 ± 0.0116</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.9270 ± 0.0453</t>
+          <t>0.9774 ± 0.0252</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4542857142857143</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05198290317231447</v>
+        <v>0.02373321103690879</v>
       </c>
       <c r="P9" t="n">
-        <v>0.381188188267436</v>
+        <v>0.3288815459430735</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.06749667957709082</v>
+        <v>0.04181276949365909</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4459420829741657</v>
+        <v>0.360034188034188</v>
       </c>
       <c r="S9" t="n">
-        <v>0.07442553174320657</v>
+        <v>0.03692765966425206</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3351351351351352</v>
+        <v>0.3032258064516129</v>
       </c>
       <c r="U9" t="n">
-        <v>0.06858690562405147</v>
+        <v>0.04607373179705065</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.4667 ± 0.0520</t>
+          <t>0.4543 ± 0.0237</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.3812 ± 0.0675</t>
+          <t>0.3289 ± 0.0418</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.4459 ± 0.0744</t>
+          <t>0.3600 ± 0.0369</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.3351 ± 0.0686</t>
+          <t>0.3032 ± 0.0461</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>0.472</v>
+        <v>0.4885714285714285</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.5556864722653376</v>
+        <v>0.6090857645242369</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.5025580232930629</v>
+        <v>0.541941556809204</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.5918918918918918</v>
+        <v>0.6741935483870969</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -4559,108 +4559,108 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.916</v>
+        <v>0.9328571428571429</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02924228293261507</v>
+        <v>0.009147320339189774</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9106235622271077</v>
+        <v>0.9291236127057022</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03519628885402667</v>
+        <v>0.009571073413954689</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9512569712569713</v>
+        <v>0.8726797385620916</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04457152412772801</v>
+        <v>0.01244948101449847</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8783783783783784</v>
+        <v>0.9935483870967744</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06756756756756757</v>
+        <v>0.0129032258064516</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.9160 ± 0.0292</t>
+          <t>0.9329 ± 0.0091</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.9106 ± 0.0352</t>
+          <t>0.9291 ± 0.0096</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.9513 ± 0.0446</t>
+          <t>0.8727 ± 0.0124</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.8784 ± 0.0676</t>
+          <t>0.9935 ± 0.0129</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0.5200000000000001</v>
+        <v>0.5157142857142857</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04216370213557839</v>
+        <v>0.02065261756400137</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4672312094126575</v>
+        <v>0.4543135675381752</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.04261969382271548</v>
+        <v>0.01379532248949963</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5185386059065147</v>
+        <v>0.4542118768328446</v>
       </c>
       <c r="S10" t="n">
-        <v>0.05039762825351469</v>
+        <v>0.02210798102124477</v>
       </c>
       <c r="T10" t="n">
-        <v>0.427027027027027</v>
+        <v>0.4548387096774193</v>
       </c>
       <c r="U10" t="n">
-        <v>0.04490066952928689</v>
+        <v>0.009677419354838717</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.5200 ± 0.0422</t>
+          <t>0.5157 ± 0.0207</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.4672 ± 0.0426</t>
+          <t>0.4543 ± 0.0138</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.5185 ± 0.0504</t>
+          <t>0.4542 ± 0.0221</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.4270 ± 0.0449</t>
+          <t>0.4548 ± 0.0097</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>0.3959999999999999</v>
+        <v>0.4171428571428573</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.4433923528144502</v>
+        <v>0.474810045167527</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.4327183653504566</v>
+        <v>0.4184678617292469</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.4513513513513514</v>
+        <v>0.5387096774193552</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -4671,108 +4671,108 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.9142857142857143</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04580150409951377</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9091850229600009</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="E11" t="n">
-        <v>0.04235604543369281</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.889508683313031</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06924353342860282</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9324324324324325</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02769446152962055</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.9067 ± 0.0458</t>
+          <t>0.9143 ± 0.0000</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.9092 ± 0.0424</t>
+          <t>0.8929 ± 0.0000</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.8895 ± 0.0692</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.9324 ± 0.0277</t>
+          <t>0.8065 ± 0.0000</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0.5093333333333333</v>
+        <v>0.4142857142857143</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02133333333333333</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4917474116830446</v>
+        <v>0.2545454545454545</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.04548098950173056</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5019145190771878</v>
+        <v>0.2916666666666666</v>
       </c>
       <c r="S11" t="n">
-        <v>0.021382753854929</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4864864864864865</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="U11" t="n">
-        <v>0.07644397634449161</v>
+        <v>2.775557561562891e-17</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.5093 ± 0.0213</t>
+          <t>0.4143 ± 0.0000</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.4917 ± 0.0455</t>
+          <t>0.2545 ± 0.0000</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.5019 ± 0.0214</t>
+          <t>0.2917 ± 0.0000</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.4865 ± 0.0764</t>
+          <t>0.2258 ± 0.0000</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>0.3973333333333333</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.4174376112769563</v>
+        <v>0.6383116883116884</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.3875941642358433</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.4459459459459459</v>
+        <v>0.5806451612903225</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -4949,95 +4949,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SVM-RBF</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9573333333333333</v>
+        <v>0.9857142857142858</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01959591794226543</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9549442804586885</v>
+        <v>0.984126984126984</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02156270877056382</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9886418351124234</v>
+        <v>0.96875</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01392151593083359</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9243243243243244</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03783783783783785</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.9573 ± 0.0196</t>
+          <t>0.9857 ± 0.0000</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.9549 ± 0.0216</t>
+          <t>0.9841 ± 0.0000</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.9886 ± 0.0139</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.9243 ± 0.0378</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.9573333333333333</v>
+        <v>0.9857142857142858</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01959591794226543</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9549442804586885</v>
+        <v>0.984126984126984</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02156270877056382</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9886418351124234</v>
+        <v>0.96875</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01392151593083359</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9243243243243244</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03783783783783785</v>
+        <v>0</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.9573 ± 0.0196</t>
+          <t>0.9857 ± 0.0000</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.9549 ± 0.0216</t>
+          <t>0.9841 ± 0.0000</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.9886 ± 0.0139</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.9243 ± 0.0378</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="Z2" t="n">
@@ -5061,108 +5061,108 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM-RBF</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9559999999999998</v>
+        <v>0.9857142857142858</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02235073948565364</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9533200486764233</v>
+        <v>0.984126984126984</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02507909177402514</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9886418351124234</v>
+        <v>0.96875</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01392151593083359</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9216216216216218</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04432762018069385</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.9560 ± 0.0224</t>
+          <t>0.9857 ± 0.0000</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.9533 ± 0.0251</t>
+          <t>0.9841 ± 0.0000</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.9886 ± 0.0139</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.9216 ± 0.0443</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.9573333333333333</v>
+        <v>0.9857142857142858</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01959591794226543</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9549442804586885</v>
+        <v>0.984126984126984</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.02156270877056382</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9886418351124234</v>
+        <v>0.96875</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01392151593083359</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9243243243243244</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03783783783783785</v>
+        <v>0</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.9573 ± 0.0196</t>
+          <t>0.9857 ± 0.0000</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.9549 ± 0.0216</t>
+          <t>0.9841 ± 0.0000</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.9886 ± 0.0139</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.9243 ± 0.0378</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>-0.001333333333333409</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.001624231782265229</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.002702702702702675</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
@@ -5173,105 +5173,105 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NaiveBayes</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9546666666666667</v>
+        <v>0.9771428571428572</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0170749979664876</v>
+        <v>0.006998542122237681</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9526820073843034</v>
+        <v>0.9749007936507936</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01853939000672906</v>
+        <v>0.007533152978797446</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9775705964096056</v>
+        <v>0.9511363636363637</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01630136615858147</v>
+        <v>0.01438147386861333</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9297297297297298</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03243243243243243</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.9547 ± 0.0171</t>
+          <t>0.9771 ± 0.0070</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.9527 ± 0.0185</t>
+          <t>0.9749 ± 0.0075</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.9776 ± 0.0163</t>
+          <t>0.9511 ± 0.0144</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.9297 ± 0.0324</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.9506666666666668</v>
+        <v>0.9571428571428571</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01982142499642468</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9488340101644223</v>
+        <v>0.9538461538461538</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02099408233403052</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9696699246699246</v>
+        <v>0.9117647058823529</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02511257901514386</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9297297297297298</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03243243243243243</v>
+        <v>0</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.9507 ± 0.0198</t>
+          <t>0.9571 ± 0.0000</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.9488 ± 0.0210</t>
+          <t>0.9538 ± 0.0000</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.9697 ± 0.0251</t>
+          <t>0.9118 ± 0.0000</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.9297 ± 0.0324</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>0.003999999999999893</v>
+        <v>0.02000000000000013</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.003847997219881161</v>
+        <v>0.02105463980463984</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.007900671739681009</v>
+        <v>0.03937165775401075</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -5285,108 +5285,108 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>NaiveBayes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9533333333333331</v>
+        <v>0.9714285714285713</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01366260102127946</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9513798805474434</v>
+        <v>0.96875</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01493412066788913</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9752040740430834</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01902222469328762</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9297297297297298</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03243243243243243</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.9533 ± 0.0137</t>
+          <t>0.9714 ± 0.0000</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.9514 ± 0.0149</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.9752 ± 0.0190</t>
+          <t>0.9394 ± 0.0000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.9297 ± 0.0324</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.9613333333333334</v>
+        <v>0.9714285714285713</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01833030277982337</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9593753143373979</v>
+        <v>0.96875</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01982438504397334</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9887212001917887</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01382508701882397</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9324324324324325</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03471684480720305</v>
+        <v>0</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.9613 ± 0.0183</t>
+          <t>0.9714 ± 0.0000</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.9594 ± 0.0198</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.9887 ± 0.0138</t>
+          <t>0.9394 ± 0.0000</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.9324 ± 0.0347</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>-0.008000000000000229</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.007995433789954487</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.01351712614870526</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.002702702702702675</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -5397,108 +5397,108 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>GradientBoost</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9493333333333334</v>
+        <v>0.9714285714285713</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0258542925728871</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9471443985093639</v>
+        <v>0.96875</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02807031046294366</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9674413598097809</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02864768705787136</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9297297297297298</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05012766754322002</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.9493 ± 0.0259</t>
+          <t>0.9714 ± 0.0000</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.9471 ± 0.0281</t>
+          <t>0.9688 ± 0.0000</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.9674 ± 0.0286</t>
+          <t>0.9394 ± 0.0000</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.9297 ± 0.0501</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.9613333333333334</v>
+        <v>0.9571428571428571</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01392040867854741</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9597232349628644</v>
+        <v>0.9538461538461538</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01496877976938839</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9835374073764166</v>
+        <v>0.9117647058823529</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01788472955671827</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9378378378378379</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02972972972972974</v>
+        <v>0</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.9613 ± 0.0139</t>
+          <t>0.9571 ± 0.0000</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.9597 ± 0.0150</t>
+          <t>0.9538 ± 0.0000</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.9835 ± 0.0179</t>
+          <t>0.9118 ± 0.0000</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.9378 ± 0.0297</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>-0.01200000000000001</v>
+        <v>0.01428571428571423</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.01257883645350044</v>
+        <v>0.01490384615384621</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.01609604756663574</v>
+        <v>0.02762923351158653</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.008108108108108136</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -5513,104 +5513,104 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9479999999999998</v>
+        <v>0.9585714285714285</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01627540748764492</v>
+        <v>0.007693092581620716</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9457327984769963</v>
+        <v>0.9553817016317018</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01805025421338715</v>
+        <v>0.007934334836083086</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9695691534081627</v>
+        <v>0.9146855105678636</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01907251128167408</v>
+        <v>0.01456043433314883</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9243243243243244</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03783783783783785</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.9480 ± 0.0163</t>
+          <t>0.9586 ± 0.0077</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.9457 ± 0.0181</t>
+          <t>0.9554 ± 0.0079</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.9696 ± 0.0191</t>
+          <t>0.9147 ± 0.0146</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.9243 ± 0.0378</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0.9653333333333333</v>
+        <v>0.9671428571428571</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01359738536958078</v>
+        <v>0.009147320339189774</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9639988000734674</v>
+        <v>0.96432615995116</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01427518868765128</v>
+        <v>0.009639743532762493</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9860274560274561</v>
+        <v>0.9312778520499109</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01397856672567184</v>
+        <v>0.01804596280141018</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9432432432432434</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02245033476464344</v>
+        <v>0</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.9653 ± 0.0136</t>
+          <t>0.9671 ± 0.0091</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9640 ± 0.0143</t>
+          <t>0.9643 ± 0.0096</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.9860 ± 0.0140</t>
+          <t>0.9313 ± 0.0180</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.9432 ± 0.0225</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>-0.01733333333333342</v>
+        <v>-0.008571428571428563</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.01826600159647107</v>
+        <v>-0.008944458319458226</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.01645830261929337</v>
+        <v>-0.01659234148204725</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.01891891891891895</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -5621,108 +5621,108 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GradientBoost</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9453333333333334</v>
+        <v>0.9571428571428571</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02186829262247564</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9434358295745456</v>
+        <v>0.9538461538461538</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02290830453192941</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9621073821073821</v>
+        <v>0.9117647058823529</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03145211250564695</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.927027027027027</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03831742399664279</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.9453 ± 0.0219</t>
+          <t>0.9571 ± 0.0000</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.9434 ± 0.0229</t>
+          <t>0.9538 ± 0.0000</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.9621 ± 0.0315</t>
+          <t>0.9118 ± 0.0000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.9270 ± 0.0383</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.9613333333333334</v>
+        <v>0.9571428571428571</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01733333333333335</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9594184718330967</v>
+        <v>0.9538461538461538</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01859936423559992</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9887212001917887</v>
+        <v>0.9117647058823529</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01382508701882397</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9324324324324325</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03254485021295216</v>
+        <v>0</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.9613 ± 0.0173</t>
+          <t>0.9571 ± 0.0000</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.9594 ± 0.0186</t>
+          <t>0.9538 ± 0.0000</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.9887 ± 0.0138</t>
+          <t>0.9118 ± 0.0000</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.9324 ± 0.0325</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>-0.01600000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.01598264225855106</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.02661381808440655</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.005405405405405461</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -5737,104 +5737,104 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9386666666666666</v>
+        <v>0.9428571428571428</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02809507667427396</v>
+        <v>0.01106566670344977</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9368746605327736</v>
+        <v>0.9379673104673104</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0301395105853278</v>
+        <v>0.01258359015036446</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9485001062672286</v>
+        <v>0.9019757448433919</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03246548163303751</v>
+        <v>0.01157231801869656</v>
       </c>
       <c r="H9" t="n">
-        <v>0.927027027027027</v>
+        <v>0.9774193548387098</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04530555301146002</v>
+        <v>0.02519435379324729</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.9387 ± 0.0281</t>
+          <t>0.9429 ± 0.0111</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.9369 ± 0.0301</t>
+          <t>0.9380 ± 0.0126</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.9485 ± 0.0325</t>
+          <t>0.9020 ± 0.0116</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.9270 ± 0.0453</t>
+          <t>0.9774 ± 0.0252</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.9626666666666667</v>
+        <v>0.9342857142857144</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02048305532764963</v>
+        <v>0.01829464067837958</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9614029655741019</v>
+        <v>0.9291201050574693</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02119837818684929</v>
+        <v>0.01897011088793063</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9781359532907519</v>
+        <v>0.8920485144204309</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02363022285354803</v>
+        <v>0.03259370079531765</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9459459459459459</v>
+        <v>0.9709677419354839</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0319788096383763</v>
+        <v>0.0304321972001826</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.9627 ± 0.0205</t>
+          <t>0.9343 ± 0.0183</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.9614 ± 0.0212</t>
+          <t>0.9291 ± 0.0190</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.9781 ± 0.0236</t>
+          <t>0.8920 ± 0.0326</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.9459 ± 0.0320</t>
+          <t>0.9710 ± 0.0304</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>-0.02400000000000002</v>
+        <v>0.008571428571428452</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.0245283050413283</v>
+        <v>0.008847205409841075</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.02963584702352329</v>
+        <v>0.009927230422961064</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.01891891891891895</v>
+        <v>0.006451612903225934</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -5845,108 +5845,108 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.916</v>
+        <v>0.9328571428571429</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02924228293261507</v>
+        <v>0.009147320339189774</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9106235622271077</v>
+        <v>0.9291236127057022</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03519628885402667</v>
+        <v>0.009571073413954689</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9512569712569713</v>
+        <v>0.8726797385620916</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04457152412772801</v>
+        <v>0.01244948101449847</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8783783783783784</v>
+        <v>0.9935483870967744</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06756756756756757</v>
+        <v>0.0129032258064516</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.9160 ± 0.0292</t>
+          <t>0.9329 ± 0.0091</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.9106 ± 0.0352</t>
+          <t>0.9291 ± 0.0096</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.9513 ± 0.0446</t>
+          <t>0.8727 ± 0.0124</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.8784 ± 0.0676</t>
+          <t>0.9935 ± 0.0129</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.8785714285714287</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0304046780026437</v>
+        <v>0.02575393768188564</v>
       </c>
       <c r="P10" t="n">
-        <v>0.942560698600406</v>
+        <v>0.8800095564745828</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.03419752504743662</v>
+        <v>0.0225762954145012</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9881840449582384</v>
+        <v>0.7864589646885076</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01452403234957743</v>
+        <v>0.03620129452112127</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9027027027027028</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0582179979149676</v>
+        <v>0</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.9467 ± 0.0304</t>
+          <t>0.8786 ± 0.0258</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.9426 ± 0.0342</t>
+          <t>0.8800 ± 0.0226</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.9882 ± 0.0145</t>
+          <t>0.7865 ± 0.0362</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.9027 ± 0.0582</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>-0.03066666666666662</v>
+        <v>0.05428571428571427</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.03193713637329831</v>
+        <v>0.04911405623111942</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.03692707370126713</v>
+        <v>0.08622077387358396</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.02432432432432441</v>
+        <v>-0.006451612903225601</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -5957,108 +5957,108 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.9142857142857143</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04580150409951377</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9091850229600009</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="E11" t="n">
-        <v>0.04235604543369281</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.889508683313031</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06924353342860282</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9324324324324325</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02769446152962055</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.9067 ± 0.0458</t>
+          <t>0.9143 ± 0.0000</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.9092 ± 0.0424</t>
+          <t>0.8929 ± 0.0000</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.8895 ± 0.0692</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.9324 ± 0.0277</t>
+          <t>0.8065 ± 0.0000</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0.9186666666666667</v>
+        <v>0.8714285714285716</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02490872225635921</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9170030677621485</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.02635851876379843</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9219388885874954</v>
+        <v>0.84375</v>
       </c>
       <c r="S11" t="n">
-        <v>0.03039795167188453</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9135135135135135</v>
+        <v>0.8709677419354838</v>
       </c>
       <c r="U11" t="n">
-        <v>0.04151970674523572</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.9187 ± 0.0249</t>
+          <t>0.8714 ± 0.0000</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.9170 ± 0.0264</t>
+          <t>0.8571 ± 0.0000</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.9219 ± 0.0304</t>
+          <t>0.8438 ± 0.0000</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.9135 ± 0.0415</t>
+          <t>0.8710 ± 0.0000</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>-0.01200000000000012</v>
+        <v>0.0428571428571427</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.007818044802147539</v>
+        <v>0.03571428571428581</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.03243020527446439</v>
+        <v>0.15625</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.01891891891891895</v>
+        <v>-0.06451612903225801</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
